--- a/backend/order/src/test/resources/workbooks/DS-ORDER-3X/monthly/monthly_forecast_jan.xlsx
+++ b/backend/order/src/test/resources/workbooks/DS-ORDER-3X/monthly/monthly_forecast_jan.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Forecast</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
